--- a/data/performance/daily/signal_list_2026-05-14.xlsx
+++ b/data/performance/daily/signal_list_2026-05-14.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 27.2%  (25W / 67L of 92 evaluated)</t>
+          <t>Win Rate: 31.5%  (29W / 63L of 92 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1630</v>
+        <v>1640</v>
       </c>
       <c r="D6" t="n">
         <v>1600</v>
@@ -595,10 +595,10 @@
         <v>1630</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.84</v>
+        <v>-2.44</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4380</v>
+        <v>4400</v>
       </c>
       <c r="D8" t="n">
         <v>4250</v>
@@ -679,10 +679,10 @@
         <v>4390</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.97</v>
+        <v>-3.41</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>532.4</v>
+        <v>585</v>
       </c>
       <c r="D10" t="n">
         <v>523.38</v>
@@ -763,10 +763,10 @@
         <v>532.4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>-8.99</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.69</v>
+        <v>-10.53</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3310</v>
+        <v>3340</v>
       </c>
       <c r="D11" t="n">
         <v>3180</v>
@@ -805,10 +805,10 @@
         <v>3320</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.93</v>
+        <v>-4.79</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2290</v>
+        <v>2270</v>
       </c>
       <c r="D12" t="n">
         <v>2310</v>
@@ -847,10 +847,10 @@
         <v>2380</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.93</v>
+        <v>4.85</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.87</v>
+        <v>1.76</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D15" t="n">
         <v>1600</v>
@@ -973,10 +973,10 @@
         <v>1630</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.84</v>
+        <v>-2.14</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="D17" t="n">
         <v>2380</v>
@@ -1057,14 +1057,14 @@
         <v>2390</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.84</v>
+        <v>0.42</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17200</v>
+        <v>17225</v>
       </c>
       <c r="D18" t="n">
         <v>16675</v>
@@ -1099,10 +1099,10 @@
         <v>17200</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.05</v>
+        <v>-3.19</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="D19" t="n">
         <v>1200</v>
@@ -1141,10 +1141,10 @@
         <v>1240</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.83</v>
+        <v>-2.44</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D22" t="n">
         <v>147</v>
@@ -1267,10 +1267,10 @@
         <v>160</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.9</v>
+        <v>5.96</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.55</v>
+        <v>-2.65</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5700</v>
+        <v>5875</v>
       </c>
       <c r="D23" t="n">
         <v>5350</v>
@@ -1309,10 +1309,10 @@
         <v>5700</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0</v>
+        <v>-2.98</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.14</v>
+        <v>-8.94</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2590</v>
+        <v>2540</v>
       </c>
       <c r="D24" t="n">
         <v>2530</v>
@@ -1351,10 +1351,10 @@
         <v>2600</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.39</v>
+        <v>2.36</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.32</v>
+        <v>-0.39</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D25" t="n">
         <v>635</v>
@@ -1393,10 +1393,10 @@
         <v>700</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.7</v>
+        <v>16.67</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.96</v>
+        <v>5.83</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6025</v>
+        <v>6125</v>
       </c>
       <c r="D29" t="n">
         <v>5925</v>
@@ -1561,10 +1561,10 @@
         <v>6025</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.66</v>
+        <v>-3.27</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D31" t="n">
         <v>980</v>
@@ -1645,10 +1645,10 @@
         <v>1015</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.45</v>
+        <v>-3.92</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D32" t="n">
         <v>254</v>
@@ -1687,10 +1687,10 @@
         <v>262</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.77</v>
+        <v>-1.5</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.31</v>
+        <v>-4.51</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1115.82</v>
+        <v>1230</v>
       </c>
       <c r="D35" t="n">
         <v>1075</v>
@@ -1813,10 +1813,10 @@
         <v>1115.82</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.66</v>
+        <v>-12.6</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13000</v>
+        <v>13150</v>
       </c>
       <c r="D37" t="n">
         <v>12775</v>
@@ -1897,10 +1897,10 @@
         <v>13000</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-1.73</v>
+        <v>-2.85</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D38" t="n">
         <v>535</v>
@@ -1939,10 +1939,10 @@
         <v>560</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-3.6</v>
+        <v>-4.46</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D39" t="n">
         <v>420</v>
@@ -1981,10 +1981,10 @@
         <v>420</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2750</v>
+        <v>2550</v>
       </c>
       <c r="D41" t="n">
         <v>2670</v>
@@ -2065,14 +2065,14 @@
         <v>2890</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5.09</v>
+        <v>13.33</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.71</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D42" t="n">
         <v>122</v>
@@ -2107,10 +2107,10 @@
         <v>129</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.78</v>
+        <v>1.57</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-4.69</v>
+        <v>-3.94</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6850</v>
+        <v>6875</v>
       </c>
       <c r="D45" t="n">
         <v>6575</v>
@@ -2233,10 +2233,10 @@
         <v>6900</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.73</v>
+        <v>0.36</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-4.01</v>
+        <v>-4.36</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D48" t="n">
         <v>127</v>
@@ -2359,10 +2359,10 @@
         <v>130</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.79</v>
+        <v>1.6</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D49" t="n">
         <v>92</v>
@@ -2401,10 +2401,10 @@
         <v>98</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>11.36</v>
+        <v>12.64</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="D51" t="n">
         <v>1945</v>
@@ -2485,10 +2485,10 @@
         <v>1965</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-1.02</v>
+        <v>-1.27</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D53" t="n">
         <v>166</v>
@@ -2569,10 +2569,10 @@
         <v>174</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>7.41</v>
+        <v>5.45</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>2.47</v>
+        <v>0.61</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>965</v>
+        <v>880</v>
       </c>
       <c r="D54" t="n">
         <v>945</v>
@@ -2611,14 +2611,14 @@
         <v>965</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0</v>
+        <v>9.66</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.39</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D55" t="n">
         <v>37</v>
@@ -2653,10 +2653,10 @@
         <v>37</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>19.35</v>
+        <v>8.82</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>19.35</v>
+        <v>8.82</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D56" t="n">
         <v>240</v>
@@ -2695,10 +2695,10 @@
         <v>240</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>13.21</v>
+        <v>2.56</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>13.21</v>
+        <v>2.56</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D57" t="n">
         <v>97</v>
@@ -2737,10 +2737,10 @@
         <v>104</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-6.73</v>
+        <v>-7.62</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" t="n">
         <v>89</v>
@@ -2821,10 +2821,10 @@
         <v>95</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1.06</v>
+        <v>2.15</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-5.32</v>
+        <v>-4.3</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D60" t="n">
         <v>224</v>
@@ -2863,10 +2863,10 @@
         <v>232</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-2.61</v>
+        <v>-3.45</v>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4700</v>
+        <v>4710</v>
       </c>
       <c r="D62" t="n">
         <v>4600</v>
@@ -2947,10 +2947,10 @@
         <v>4720</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-2.13</v>
+        <v>-2.34</v>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D63" t="n">
         <v>38</v>
@@ -2989,10 +2989,10 @@
         <v>38</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0</v>
+        <v>-7.32</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>0</v>
+        <v>-7.32</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="D65" t="n">
         <v>1010</v>
@@ -3073,10 +3073,10 @@
         <v>1010</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1</v>
+        <v>2.02</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>1</v>
+        <v>2.02</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66" t="n">
         <v>100</v>
@@ -3115,10 +3115,10 @@
         <v>106</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>10.42</v>
+        <v>11.58</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4.17</v>
+        <v>5.26</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D68" t="n">
         <v>71</v>
@@ -3199,10 +3199,10 @@
         <v>76</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-6.58</v>
+        <v>-7.79</v>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D69" t="n">
         <v>414</v>
@@ -3241,10 +3241,10 @@
         <v>422</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-1.9</v>
+        <v>-2.82</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D70" t="n">
         <v>52</v>
@@ -3283,14 +3283,14 @@
         <v>52</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>8.33</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1815</v>
+        <v>2000</v>
       </c>
       <c r="D71" t="n">
         <v>1800</v>
@@ -3325,10 +3325,10 @@
         <v>1885</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3.86</v>
+        <v>-5.75</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-0.83</v>
+        <v>-10</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="D73" t="n">
         <v>965</v>
@@ -3409,10 +3409,10 @@
         <v>985</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>-1.03</v>
+        <v>-0.52</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="D74" t="n">
         <v>342</v>
@@ -3451,10 +3451,10 @@
         <v>342</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.59</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0.59</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D75" t="n">
         <v>82</v>
@@ -3493,10 +3493,10 @@
         <v>88</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>8.640000000000001</v>
+        <v>10</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D78" t="n">
         <v>117</v>
@@ -3619,14 +3619,14 @@
         <v>126</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2.44</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-4.88</v>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.86</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D80" t="n">
         <v>80</v>
@@ -3703,14 +3703,14 @@
         <v>86</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>6.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.27</v>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D81" t="n">
         <v>66</v>
@@ -3745,10 +3745,10 @@
         <v>66</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D82" t="n">
         <v>157</v>
@@ -3787,10 +3787,10 @@
         <v>165</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2.48</v>
+        <v>3.12</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-2.48</v>
+        <v>-1.88</v>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="D87" t="n">
         <v>402</v>
@@ -3997,10 +3997,10 @@
         <v>406</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>5.18</v>
+        <v>9.73</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>4.15</v>
+        <v>8.65</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="D88" t="n">
         <v>985</v>
@@ -4039,14 +4039,14 @@
         <v>1015</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2.53</v>
+        <v>3.57</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.51</v>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D90" t="n">
         <v>80</v>
@@ -4123,10 +4123,10 @@
         <v>87</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>17.57</v>
+        <v>16</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>8.109999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D92" t="n">
         <v>137</v>
@@ -4207,10 +4207,10 @@
         <v>144</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-3.52</v>
+        <v>-2.84</v>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="D94" t="n">
         <v>595</v>
@@ -4291,14 +4291,14 @@
         <v>595</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.85</v>
+        <v>-0.83</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.83</v>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2500</v>
+        <v>2520</v>
       </c>
       <c r="D96" t="n">
         <v>2460</v>
@@ -4375,10 +4375,10 @@
         <v>2510</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-1.6</v>
+        <v>-2.38</v>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
